--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29BB1CA7-F0C8-417B-A2CE-206575BDAA88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC29C325-BCEB-4404-B7E7-9A1EF91C3D82}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABF360FE-4467-45E4-BF86-C15C0FCA51AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35317548-0137-45F8-97DD-253A803B6308}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{798E8E6A-F196-4251-B3C7-265A79B0BDCA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4F547D3-DDEC-466A-B60E-9EF2EDAA9FBA}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC29C325-BCEB-4404-B7E7-9A1EF91C3D82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AF2AA75-729A-48FB-B837-7470ECDCC183}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35317548-0137-45F8-97DD-253A803B6308}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCFAAC0-F1A7-4FA3-9821-F2C78CF3DE80}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4F547D3-DDEC-466A-B60E-9EF2EDAA9FBA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A883C999-2A75-4420-9D2B-39DA297521A5}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AF2AA75-729A-48FB-B837-7470ECDCC183}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECAB333-187C-4B3D-B03D-F274ADB43187}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCFAAC0-F1A7-4FA3-9821-F2C78CF3DE80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0601F78F-A3A4-45F2-97A1-DA53EEB8F2F3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A883C999-2A75-4420-9D2B-39DA297521A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79823B13-50E5-480D-901B-DDE5413AD4FD}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECAB333-187C-4B3D-B03D-F274ADB43187}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50CD1E87-72B1-4412-84EA-EB02B8CB826C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0601F78F-A3A4-45F2-97A1-DA53EEB8F2F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9EA673E-4269-409B-9C42-4B8AEA9FF6E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79823B13-50E5-480D-901B-DDE5413AD4FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68EFE11-0902-4239-84BC-7E9F37A6116F}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -11,6 +11,215 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>vocal_repertoire_types</t>
+  </si>
+  <si>
+    <t>vocal_repertoire_types_Source</t>
+  </si>
+  <si>
+    <t>Ateles chamek</t>
+  </si>
+  <si>
+    <t>Dubreuil, C., Notman, H., &amp; Pavelka, M. S. (2015). Sex differences in the use of whinny vocalizations in spider monkeys (Ateles geoffroyi). International Journal of Primatology, 36(2), 412-428.</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
+  </si>
+  <si>
+    <t>Cebus capucinus</t>
+  </si>
+  <si>
+    <t>Gros-Louis, J. J., Perry, S. E., Fichtel, C., Wikberg, E., Gilkenson, H., Wofsy, S., &amp; Fuentes, A. (2008). Vocal repertoire of Cebus capucinus: acoustic structure, context, and usage. International Journal of Primatology, 29(3), 641-670.</t>
+  </si>
+  <si>
+    <t>Cercopithecus diana</t>
+  </si>
+  <si>
+    <t>Magnuson (unpub) (ATWP)</t>
+  </si>
+  <si>
+    <t>Chlorocebus sabaeus</t>
+  </si>
+  <si>
+    <t>Galat Gérard. (1975). Eco-ethologie de Cercopithecus sabaeus en limite d'aire au Sénégal : rapport d'élève de 2ème année. Dakar : ORSTOM, 215 p. multigr.</t>
+  </si>
+  <si>
+    <t>Colobus polykomos</t>
+  </si>
+  <si>
+    <t>Walek, M. L. (1978). Vocalizations of the black and white colobus monkey (Colobus polykomos Zimmerman 1780). American Journal of Physical Anthropology, 49(2), 227-239.</t>
+  </si>
+  <si>
+    <t>Eulemur coronatus</t>
+  </si>
+  <si>
+    <t>Gamba, M., Friard, O., Riondato, I., Righini, R., Colombo, C., Miaretsoa, L., ... &amp; Giacoma, C. (2015). Comparative analysis of the vocal repertoire of Eulemur: a dynamic time warping approach. International Journal of Primatology, 36(5), 894-910.</t>
+  </si>
+  <si>
+    <t>Eulemur flavifrons</t>
+  </si>
+  <si>
+    <t>Eulemur fulvus</t>
+  </si>
+  <si>
+    <t>Eulemur macaco</t>
+  </si>
+  <si>
+    <t>Eulemur mongoz</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Baldwin, L.A. &amp; Teleki, G. (1976). Patterns of gibbon behavior on Hall’s Island, Bermuda: a preliminary ethogram for Hylobates lar. — In: Gibbon and Siamang. Vol. 4: suspensory behavior, locomotion, and other behaviors of captive gibbons; cognition (Rumbaugh, D.M., ed.). Karger, Basel, p. 21-105.</t>
+  </si>
+  <si>
+    <t>Hylobates moloch</t>
+  </si>
+  <si>
+    <t>Hylobates muelleri</t>
+  </si>
+  <si>
+    <t>Lagothrix lagothricha</t>
+  </si>
+  <si>
+    <t>Lagothrix lagotricha</t>
+  </si>
+  <si>
+    <t>Lemur catta</t>
+  </si>
+  <si>
+    <t>Macedonia, J. M. (1993). The vocal repertoire of the ringtailed lemur (Lemur catta). Folia primatologica, 61(4), 186-217.</t>
+  </si>
+  <si>
+    <t>Leontopithecus rosalia</t>
+  </si>
+  <si>
+    <t>McLanahan, E. B. &amp; K. M. Green, 1977. The vocal repertoire and an analysis of the context vocalization in Leontopithecus rosalia. In: Biology and Conservation of the Callitrichidae, Devra G. Kleiman (ed.), Smithsonian Inst. Press, Washington, D.C., pp. 251–270.</t>
+  </si>
+  <si>
+    <t>Macaca fascicularis</t>
+  </si>
+  <si>
+    <t>Palombit, R. A. (1992). A preliminary study of vocal communication in wild long-tailed macaques (Macaca fascicularis). I. Vocal repertoire and call emission. International Journal of Primatology, 13(2), 143.</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Hauser, M. D., &amp; Marler, P. (1993). Food-associated calls in rhesus macaques (Macaca mulatta): I. Socioecological factors. Behavioral Ecology, 4(3), 194-205.</t>
+  </si>
+  <si>
+    <t>Macaca silenus</t>
+  </si>
+  <si>
+    <t>Hohmann, G. (1991). Comparative analyses of age-and sex-specific patterns of vocal behaviour in four species of old world monkeys. Folia Primatologica, 56(3), 133-156.</t>
+  </si>
+  <si>
+    <t>Macaca sylvanus</t>
+  </si>
+  <si>
+    <t>Fischer, J., &amp; Hammerschmidt, K. (2002). An overview of the Barbary macaque, Macaca sylvanus, vocal repertoire. Folia Primatologica, 73(1), 32-45.</t>
+  </si>
+  <si>
+    <t>Macaca tonkeana</t>
+  </si>
+  <si>
+    <t>Masataka, N., &amp; Thierry, B. (1993). Vocal communication of Tonkean macaques in confined environments. Primates, 34(2), 169-180.</t>
+  </si>
+  <si>
+    <t>Nomascus leucogenys</t>
+  </si>
+  <si>
+    <t>Eichler, S. (2002). Das Lautrepertoire der Schopfgibbons (Gattung Nomascus). Diploma thesis, Anthropological Institute Zurich, Zurich.</t>
+  </si>
+  <si>
+    <t>Pan paniscus</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Pongo sp.</t>
+  </si>
+  <si>
+    <t>Pongo abelii</t>
+  </si>
+  <si>
+    <t>Hardus ME, Lameira AR, Singleton I, Morrogh-Bernard HC, Knott CD, et al. (2009) A description of the orangutan’s vocal and sound repertoire, with a focus on geographic variation. Orangutans: Geographic variation in behavioral ecology and conservation. New York: Oxford Univ Press. pp. 49–64.</t>
+  </si>
+  <si>
+    <t>Pongo pygmaeus</t>
+  </si>
+  <si>
+    <t>Propithecus coquereli</t>
+  </si>
+  <si>
+    <t>Patel, E.R., Anderson, J.D., Owren, M.J.. 2005. Conference Proceeding. Sex differences in the acoustic structure in a monomorphic primate: Wild silky sifakas (Propithecus candidus) of Northeastern Madagascar. American Journal of Primatology, 66(Suppl 1), 46-47</t>
+  </si>
+  <si>
+    <t>Saguinus imperator</t>
+  </si>
+  <si>
+    <t>Saguinus midas</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Di Bitetti, M. S. (2001). Food-associated calls in the tufted capuchin monkey (Cebus apella). State University of New York at Stony Brook.</t>
+  </si>
+  <si>
+    <t>Symphalangus syndactylus</t>
+  </si>
+  <si>
+    <t>Chivers, D. J. (1976). Communication within and between family groups of siamang (Symphalangus syndactylus). Behaviour, 57(1-2), 116-135.</t>
+  </si>
+  <si>
+    <t>Trachypithecus auratus</t>
+  </si>
+  <si>
+    <t>Vincent Nijman, pers. com.</t>
+  </si>
+  <si>
+    <t>Trachypithecus francoisi</t>
+  </si>
+  <si>
+    <t>Tilo Nadler (unpub) (ATWP)</t>
+  </si>
+  <si>
+    <t>Varecia rubra</t>
+  </si>
+  <si>
+    <t>Zimmermann, E. (2017). Evolutionary origins of primate vocal communication: Diversity, flexibility, and complexity of vocalizations in basal primates. In Primate hearing and communication (pp. 109-140). Springer, Cham.</t>
+  </si>
+  <si>
+    <t>Varecia variegata</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,806 +563,564 @@
   <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>vocal_repertoire_types</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>vocal_repertoire_types_Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ateles chamek</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ateles chamek</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2">
         <v>14</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Dubreuil, C., Notman, H., &amp; Pavelka, M. S. (2015). Sex differences in the use of whinny vocalizations in spider monkeys (Ateles geoffroyi). International Journal of Primatology, 36(2), 412-428.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cebus capucinus</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cebus capucinus</t>
-        </is>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
         <v>27</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Gros-Louis, J. J., Perry, S. E., Fichtel, C., Wikberg, E., Gilkenson, H., Wofsy, S., &amp; Fuentes, A. (2008). Vocal repertoire of Cebus capucinus: acoustic structure, context, and usage. International Journal of Primatology, 29(3), 641-670.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Magnuson (unpub) (ATWP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chlorocebus sabaeus</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Chlorocebus sabaeus</t>
-        </is>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
       </c>
       <c r="C6">
         <v>25</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Galat Gérard. (1975). Eco-ethologie de Cercopithecus sabaeus en limite d'aire au Sénégal : rapport d'élève de 2ème année. Dakar : ORSTOM, 215 p. multigr.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Colobus polykomos</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Colobus polykomos</t>
-        </is>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Walek, M. L. (1978). Vocalizations of the black and white colobus monkey (Colobus polykomos Zimmerman 1780). American Journal of Physical Anthropology, 49(2), 227-239.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Eulemur coronatus</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Eulemur coronatus</t>
-        </is>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Gamba, M., Friard, O., Riondato, I., Righini, R., Colombo, C., Miaretsoa, L., ... &amp; Giacoma, C. (2015). Comparative analysis of the vocal repertoire of Eulemur: a dynamic time warping approach. International Journal of Primatology, 36(5), 894-910.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Eulemur flavifrons</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Eulemur flavifrons</t>
-        </is>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
       </c>
       <c r="C9">
         <v>10</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Gamba, M., Friard, O., Riondato, I., Righini, R., Colombo, C., Miaretsoa, L., ... &amp; Giacoma, C. (2015). Comparative analysis of the vocal repertoire of Eulemur: a dynamic time warping approach. International Journal of Primatology, 36(5), 894-910.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Eulemur fulvus</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Eulemur fulvus</t>
-        </is>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
       </c>
       <c r="C10">
         <v>11</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Gamba, M., Friard, O., Riondato, I., Righini, R., Colombo, C., Miaretsoa, L., ... &amp; Giacoma, C. (2015). Comparative analysis of the vocal repertoire of Eulemur: a dynamic time warping approach. International Journal of Primatology, 36(5), 894-910.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Gamba, M., Friard, O., Riondato, I., Righini, R., Colombo, C., Miaretsoa, L., ... &amp; Giacoma, C. (2015). Comparative analysis of the vocal repertoire of Eulemur: a dynamic time warping approach. International Journal of Primatology, 36(5), 894-910.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Eulemur mongoz</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Eulemur mongoz</t>
-        </is>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
       </c>
       <c r="C12">
         <v>9</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Gamba, M., Friard, O., Riondato, I., Righini, R., Colombo, C., Miaretsoa, L., ... &amp; Giacoma, C. (2015). Comparative analysis of the vocal repertoire of Eulemur: a dynamic time warping approach. International Journal of Primatology, 36(5), 894-910.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
       </c>
       <c r="C13">
         <v>16</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
       </c>
       <c r="C14">
         <v>14</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Baldwin, L.A. &amp; Teleki, G. (1976). Patterns of gibbon behavior on Hall’s Island, Bermuda: a preliminary ethogram for Hylobates lar. — In: Gibbon and Siamang. Vol. 4: suspensory behavior, locomotion, and other behaviors of captive gibbons; cognition (Rumbaugh, D.M., ed.). Karger, Basel, p. 21-105.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Hylobates moloch</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Hylobates moloch</t>
-        </is>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Baldwin, L.A. &amp; Teleki, G. (1976). Patterns of gibbon behavior on Hall’s Island, Bermuda: a preliminary ethogram for Hylobates lar. — In: Gibbon and Siamang. Vol. 4: suspensory behavior, locomotion, and other behaviors of captive gibbons; cognition (Rumbaugh, D.M., ed.). Karger, Basel, p. 21-105.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Hylobates muelleri</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Hylobates muelleri</t>
-        </is>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
       </c>
       <c r="C16">
         <v>14</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Baldwin, L.A. &amp; Teleki, G. (1976). Patterns of gibbon behavior on Hall’s Island, Bermuda: a preliminary ethogram for Hylobates lar. — In: Gibbon and Siamang. Vol. 4: suspensory behavior, locomotion, and other behaviors of captive gibbons; cognition (Rumbaugh, D.M., ed.). Karger, Basel, p. 21-105.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lagothrix lagothricha</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Lagothrix lagotricha</t>
-        </is>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
       </c>
       <c r="C18">
         <v>22</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Macedonia, J. M. (1993). The vocal repertoire of the ringtailed lemur (Lemur catta). Folia primatologica, 61(4), 186-217.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>McLanahan, E. B. &amp; K. M. Green, 1977. The vocal repertoire and an analysis of the context vocalization in Leontopithecus rosalia. In: Biology and Conservation of the Callitrichidae, Devra G. Kleiman (ed.), Smithsonian Inst. Press, Washington, D.C., pp. 251–270.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
       </c>
       <c r="C20">
         <v>17</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Palombit, R. A. (1992). A preliminary study of vocal communication in wild long-tailed macaques (Macaca fascicularis). I. Vocal repertoire and call emission. International Journal of Primatology, 13(2), 143.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
       </c>
       <c r="C21">
         <v>18</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Hauser, M. D., &amp; Marler, P. (1993). Food-associated calls in rhesus macaques (Macaca mulatta): I. Socioecological factors. Behavioral Ecology, 4(3), 194-205.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
+      <c r="D21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
       </c>
       <c r="C22">
         <v>15</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Hohmann, G. (1991). Comparative analyses of age-and sex-specific patterns of vocal behaviour in four species of old world monkeys. Folia Primatologica, 56(3), 133-156.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
       </c>
       <c r="C23">
         <v>14</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fischer, J., &amp; Hammerschmidt, K. (2002). An overview of the Barbary macaque, Macaca sylvanus, vocal repertoire. Folia Primatologica, 73(1), 32-45.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
       </c>
       <c r="C24">
         <v>20</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Masataka, N., &amp; Thierry, B. (1993). Vocal communication of Tonkean macaques in confined environments. Primates, 34(2), 169-180.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Nomascus leucogenys</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Nomascus leucogenys</t>
-        </is>
+      <c r="D24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
       </c>
       <c r="C25">
         <v>19</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Eichler, S. (2002). Das Lautrepertoire der Schopfgibbons (Gattung Nomascus). Diploma thesis, Anthropological Institute Zurich, Zurich.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
       </c>
       <c r="C26">
         <v>38</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
       </c>
       <c r="C27">
         <v>29</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pongo sp.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Pongo abelii</t>
-        </is>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
       </c>
       <c r="C29">
         <v>17</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Hardus ME, Lameira AR, Singleton I, Morrogh-Bernard HC, Knott CD, et al. (2009) A description of the orangutan’s vocal and sound repertoire, with a focus on geographic variation. Orangutans: Geographic variation in behavioral ecology and conservation. New York: Oxford Univ Press. pp. 49–64.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
+      <c r="D29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
       </c>
       <c r="C30">
         <v>23</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Hardus ME, Lameira AR, Singleton I, Morrogh-Bernard HC, Knott CD, et al. (2009) A description of the orangutan’s vocal and sound repertoire, with a focus on geographic variation. Orangutans: Geographic variation in behavioral ecology and conservation. New York: Oxford Univ Press. pp. 49–64.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Propithecus coquereli</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Propithecus coquereli</t>
-        </is>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Patel, E.R., Anderson, J.D., Owren, M.J.. 2005. Conference Proceeding. Sex differences in the acoustic structure in a monomorphic primate: Wild silky sifakas (Propithecus candidus) of Northeastern Madagascar. American Journal of Primatology, 66(Suppl 1), 46-47</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Saguinus imperator</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Saguinus imperator</t>
-        </is>
+      <c r="D31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" t="s">
+        <v>54</v>
       </c>
       <c r="C32">
         <v>33</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Saguinus midas</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Saguinus midas</t>
-        </is>
+      <c r="D32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" t="s">
+        <v>55</v>
       </c>
       <c r="C33">
         <v>33</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
       </c>
       <c r="C34">
         <v>21</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Dunn, J. C., &amp; Smaers, J. B. (2018). Neural correlates of vocal repertoire in primates. Frontiers in neuroscience, 12, 534.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
       </c>
       <c r="C35">
         <v>31</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Di Bitetti, M. S. (2001). Food-associated calls in the tufted capuchin monkey (Cebus apella). State University of New York at Stony Brook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
+      <c r="D35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" t="s">
+        <v>59</v>
       </c>
       <c r="C36">
         <v>9</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Chivers, D. J. (1976). Communication within and between family groups of siamang (Symphalangus syndactylus). Behaviour, 57(1-2), 116-135.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Trachypithecus auratus</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Trachypithecus auratus</t>
-        </is>
+      <c r="D36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" t="s">
+        <v>61</v>
       </c>
       <c r="C37">
         <v>5</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Vincent Nijman, pers. com.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Trachypithecus francoisi</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Trachypithecus francoisi</t>
-        </is>
+      <c r="D37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" t="s">
+        <v>63</v>
       </c>
       <c r="C38">
         <v>15</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Tilo Nadler (unpub) (ATWP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Varecia rubra</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Varecia rubra</t>
-        </is>
+      <c r="D38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
       </c>
       <c r="C39">
         <v>13</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Zimmermann, E. (2017). Evolutionary origins of primate vocal communication: Diversity, flexibility, and complexity of vocalizations in basal primates. In Primate hearing and communication (pp. 109-140). Springer, Cham.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
+      <c r="D39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
       </c>
       <c r="C40">
         <v>13</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Zimmermann, E. (2017). Evolutionary origins of primate vocal communication: Diversity, flexibility, and complexity of vocalizations in basal primates. In Primate hearing and communication (pp. 109-140). Springer, Cham.</t>
-        </is>
+      <c r="D40" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1437,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50CD1E87-72B1-4412-84EA-EB02B8CB826C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB0B3198-11DA-464E-89CE-22AE293F6279}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9EA673E-4269-409B-9C42-4B8AEA9FF6E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{902F6FA4-D631-4FA0-9586-DBEF46AB08FD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68EFE11-0902-4239-84BC-7E9F37A6116F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2A83D5B-25A1-46A4-9105-11F74F9F36BE}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB0B3198-11DA-464E-89CE-22AE293F6279}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B48FE9F9-216D-4F9C-A823-B750E925E651}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{902F6FA4-D631-4FA0-9586-DBEF46AB08FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D4A68B3-7A8F-440F-8439-91C13C83BDB5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2A83D5B-25A1-46A4-9105-11F74F9F36BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7C61AC1-D0E4-4C0E-98DC-35FAB6C11168}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B48FE9F9-216D-4F9C-A823-B750E925E651}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{658B6262-588A-4850-95A3-6CAF886F593B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D4A68B3-7A8F-440F-8439-91C13C83BDB5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE6FCDE-ACC1-4F05-8FDA-9CEC032EF5EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7C61AC1-D0E4-4C0E-98DC-35FAB6C11168}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36B4726A-6291-42E0-A57B-1C6D99126090}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1126,291 +1126,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{658B6262-588A-4850-95A3-6CAF886F593B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE6FCDE-ACC1-4F05-8FDA-9CEC032EF5EC}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36B4726A-6291-42E0-A57B-1C6D99126090}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1126,4 +1126,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81DF3D19-BD00-44C6-A5AB-6808E7C36E67}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14DFE1D0-C272-441D-B8FC-4E2D27CC6C8F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EEC9CED-F702-4651-9400-0428E65229F0}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1126,291 +1126,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81DF3D19-BD00-44C6-A5AB-6808E7C36E67}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14DFE1D0-C272-441D-B8FC-4E2D27CC6C8F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EEC9CED-F702-4651-9400-0428E65229F0}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1126,4 +1126,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F677F68-A502-4FCC-9C49-93E91BE34482}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC52B704-4214-4DCD-BB03-0E6F305F1E55}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8658C3ED-BE1F-4F20-8167-7B795853CCC7}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F677F68-A502-4FCC-9C49-93E91BE34482}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43C53E04-E378-4E13-ACAB-58376069DD00}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC52B704-4214-4DCD-BB03-0E6F305F1E55}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7947D6-A60A-4CCF-9E6D-37572527BC8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8658C3ED-BE1F-4F20-8167-7B795853CCC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DAF3F03-9276-4440-8F89-D79D6368C8FD}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43C53E04-E378-4E13-ACAB-58376069DD00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5AE36FF-0D61-4820-AEAE-850FAFE811AB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7947D6-A60A-4CCF-9E6D-37572527BC8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0A4B327-9A3D-4790-A293-1519D5E819D5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DAF3F03-9276-4440-8F89-D79D6368C8FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BB859D7-C03B-4C71-A2EB-92238A3053D8}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5AE36FF-0D61-4820-AEAE-850FAFE811AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{897C87B5-893A-4EF5-A38D-BB17554084DD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0A4B327-9A3D-4790-A293-1519D5E819D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4782BB70-D673-42DE-BF71-5637FCA7200F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BB859D7-C03B-4C71-A2EB-92238A3053D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81C7CFBA-E45F-4421-A828-891C696CB11E}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{897C87B5-893A-4EF5-A38D-BB17554084DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A42D26E-4DCA-453E-9EB9-1182D36F0848}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4782BB70-D673-42DE-BF71-5637FCA7200F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31000166-ED01-41A3-A040-E04A62F0E2AF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81C7CFBA-E45F-4421-A828-891C696CB11E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B35293A2-A570-4A94-82DD-0DB8B2A27732}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A42D26E-4DCA-453E-9EB9-1182D36F0848}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6916A425-5821-4585-9C13-7FF1787D0333}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31000166-ED01-41A3-A040-E04A62F0E2AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C240D54-5D9D-46FE-8D54-6C38AB8A7555}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B35293A2-A570-4A94-82DD-0DB8B2A27732}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E3A1A6B-A581-4B12-9AC2-B24E58E57043}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1126,291 +1126,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6916A425-5821-4585-9C13-7FF1787D0333}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C240D54-5D9D-46FE-8D54-6C38AB8A7555}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E3A1A6B-A581-4B12-9AC2-B24E58E57043}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1126,4 +1126,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68093C53-F5E8-4C55-98AD-0D6B348B8879}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30B9B782-3F22-4C72-8BBE-6FF600862F06}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{126261B6-34DB-42E6-B8EE-E09CAE8D96A3}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="66">
   <si>
     <t>species_sci</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Hylobates muelleri</t>
   </si>
   <si>
-    <t>Lagothrix lagothricha</t>
-  </si>
-  <si>
     <t>Lagothrix lagotricha</t>
   </si>
   <si>
@@ -158,9 +155,6 @@
   </si>
   <si>
     <t>Papio anubis</t>
-  </si>
-  <si>
-    <t>Pongo sp.</t>
   </si>
   <si>
     <t>Pongo abelii</t>
@@ -792,7 +786,7 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -803,122 +797,122 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21">
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22">
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24">
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25">
         <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26">
         <v>38</v>
@@ -929,10 +923,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <v>29</v>
@@ -943,10 +937,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -957,52 +951,52 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C29">
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C30">
         <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <v>33</v>
@@ -1013,10 +1007,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <v>33</v>
@@ -1027,10 +1021,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C34">
         <v>21</v>
@@ -1041,86 +1035,86 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C35">
         <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1404,13 +1398,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68093C53-F5E8-4C55-98AD-0D6B348B8879}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43450382-3AE5-4808-8C56-B7FC74607BA4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30B9B782-3F22-4C72-8BBE-6FF600862F06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0C5ED56-6AD9-49E7-814E-F25265DE9949}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{126261B6-34DB-42E6-B8EE-E09CAE8D96A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A979C2-AEC5-4A0B-B96C-D18A7ED09F2F}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1398,13 +1398,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43450382-3AE5-4808-8C56-B7FC74607BA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958E3008-D4F5-46CD-8E86-0BFAF37E0B22}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0C5ED56-6AD9-49E7-814E-F25265DE9949}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{811EC264-EE89-4DEA-BB44-C620F87E3988}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A979C2-AEC5-4A0B-B96C-D18A7ED09F2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{855B7B45-9D72-4DC7-91F4-96DE01FBA4E7}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1398,13 +1398,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958E3008-D4F5-46CD-8E86-0BFAF37E0B22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1AA10F1-8644-452E-8436-D2E1FCCAA41E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{811EC264-EE89-4DEA-BB44-C620F87E3988}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6541E96E-5F50-4F13-ABEF-B5055390D9CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{855B7B45-9D72-4DC7-91F4-96DE01FBA4E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93F3FDE0-4548-4A72-9C07-A7FC97C82EE7}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1398,13 +1398,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1AA10F1-8644-452E-8436-D2E1FCCAA41E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D9AD6A-C789-46C5-9D59-A7BCB85BA03F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6541E96E-5F50-4F13-ABEF-B5055390D9CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFCC3690-228D-4672-9934-04D28A5B4E65}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93F3FDE0-4548-4A72-9C07-A7FC97C82EE7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DBEABCD-CA99-40DC-B17B-9C2D5C37457E}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1398,13 +1398,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D9AD6A-C789-46C5-9D59-A7BCB85BA03F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE238FE6-3CA3-490A-94BC-FE23CE16F6DC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFCC3690-228D-4672-9934-04D28A5B4E65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C47C0243-1D20-4B24-8C7C-89D381FD6399}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DBEABCD-CA99-40DC-B17B-9C2D5C37457E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C34349C5-61CF-41C1-B9C9-E3B17E2F57BE}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1120,291 +1120,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE238FE6-3CA3-490A-94BC-FE23CE16F6DC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C47C0243-1D20-4B24-8C7C-89D381FD6399}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C34349C5-61CF-41C1-B9C9-E3B17E2F57BE}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1120,4 +1120,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA19994-655D-4B4E-ADF5-74BCDA1FCEA8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{134E2CD5-6A36-407C-8A32-F130934B8B56}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A45B29B-4096-434B-AD70-850016C3F044}"/>
 </file>